--- a/web/public/dataset/00-rfx/02_Line_Items.xlsx
+++ b/web/public/dataset/00-rfx/02_Line_Items.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Northbridge Retail India Pvt Ltd  |  GSTIN 29AACCN4471K1ZP</t>
+          <t>Kaveri Retail India Pvt Ltd  |  GSTIN 29AACCN4471K1ZP</t>
         </is>
       </c>
     </row>
